--- a/ig/ch-term/ch-vacd-vaccines-targetdiseases-cm.xlsx
+++ b/ig/ch-term/ch-vacd-vaccines-targetdiseases-cm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -811,7 +811,7 @@
     <t>68358</t>
   </si>
   <si>
-    <t>Ervebo, Injektionslösung</t>
+    <t>Ervebo</t>
   </si>
   <si>
     <t>37109004</t>
@@ -877,7 +877,13 @@
     <t>65387</t>
   </si>
   <si>
-    <t>Gardasil 9</t>
+    <t>Gardasil 9 (Fertigspritze)</t>
+  </si>
+  <si>
+    <t>65728</t>
+  </si>
+  <si>
+    <t>Gardasil 9 (Durchstechflasche)</t>
   </si>
   <si>
     <t>66940</t>
@@ -1024,55 +1030,55 @@
     <t>69913</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 0.042 mg, Injektionsdispersion in einer Fertigspritze, Pfizer AG</t>
+    <t>Comirnaty JN.1 0.042 mg</t>
   </si>
   <si>
     <t>69912-01</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 30 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 30 µg</t>
   </si>
   <si>
     <t>69912-02</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 10 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 10 µg</t>
   </si>
   <si>
     <t>69691</t>
   </si>
   <si>
-    <t>Abrysvo, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung, Pfizer AG</t>
+    <t>Abrysvo</t>
   </si>
   <si>
     <t>69788</t>
   </si>
   <si>
-    <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml, Dispersion zur Injektion, Moderna Switzerland GmbH</t>
+    <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml</t>
   </si>
   <si>
     <t>70205</t>
   </si>
   <si>
-    <t>Spikevax LP.8.1 Moderna Switzerland GmbH</t>
+    <t>Spikevax LP.8.1</t>
   </si>
   <si>
     <t>70400</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 10 μg, Injektionsdispersion Pfizer AG</t>
+    <t>Comirnaty LP.8.1 10 µg</t>
   </si>
   <si>
     <t>70403</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 30 Mikrogramm, Injektionsdispersion in einer Fertigspritze Pfizer AG'</t>
+    <t>Comirnaty LP.8.1 30 Mikrogramm</t>
   </si>
   <si>
     <t>69863-01</t>
   </si>
   <si>
-    <t>Efluelda TIV 0.5 mL, suspension injectable en seringue pré-remplie	Sanofi-Aventis (Suisse) SA</t>
+    <t>Efluelda TIV 0.5 mL</t>
   </si>
   <si>
     <t>442438000</t>
@@ -1090,25 +1096,40 @@
     <t>69995-01</t>
   </si>
   <si>
-    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml, Injektionsdispersion	Moderna Switzerland GmbH</t>
+    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml</t>
   </si>
   <si>
     <t>69781</t>
   </si>
   <si>
-    <t>Capvaxive, Injektionslösung in Fertigspritze MSD Merck Sharp &amp; Dohme AG</t>
+    <t>Capvaxive</t>
   </si>
   <si>
     <t>70042</t>
   </si>
   <si>
-    <t>Fluarix, Injektionssuspension GlaxoSmithKline AG</t>
-  </si>
-  <si>
     <t>69992</t>
   </si>
   <si>
-    <t>Influvac 0.5 ml, Injektionssuspension in einer Fertigspritze Viatris Pharma GmbH</t>
+    <t>Influvac 0.5 ml</t>
+  </si>
+  <si>
+    <t>70144</t>
+  </si>
+  <si>
+    <t>Flucelvax</t>
+  </si>
+  <si>
+    <t>70490</t>
+  </si>
+  <si>
+    <t>Vimkunya</t>
+  </si>
+  <si>
+    <t>111864006</t>
+  </si>
+  <si>
+    <t>Chikungunya fever (disorder)</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-vacd/CodeSystem/ch-vacd-myvaccines-cs</t>
@@ -1873,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E199"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4539,95 +4560,95 @@
         <v>39</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>83</v>
+        <v>197</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C158" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C161" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>59</v>
+        <v>85</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>115</v>
+        <v>59</v>
       </c>
     </row>
     <row r="163">
@@ -4641,10 +4662,10 @@
         <v>39</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="164">
@@ -4658,10 +4679,10 @@
         <v>39</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="165">
@@ -4675,10 +4696,10 @@
         <v>39</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>125</v>
+        <v>65</v>
       </c>
     </row>
     <row r="166">
@@ -4692,61 +4713,61 @@
         <v>39</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C167" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D167" t="s" s="2">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C168" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>133</v>
+        <v>71</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="170">
@@ -4760,10 +4781,10 @@
         <v>39</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>242</v>
+        <v>138</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>243</v>
+        <v>139</v>
       </c>
     </row>
     <row r="171">
@@ -4862,10 +4883,10 @@
         <v>39</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>159</v>
+        <v>243</v>
       </c>
     </row>
     <row r="177">
@@ -4879,10 +4900,10 @@
         <v>39</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>243</v>
+        <v>159</v>
       </c>
     </row>
     <row r="178">
@@ -4890,7 +4911,7 @@
         <v>314</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>39</v>
@@ -4904,10 +4925,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>39</v>
@@ -4930,35 +4951,35 @@
         <v>39</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>320</v>
+        <v>243</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D181" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="B181" t="s" s="2">
+      <c r="E181" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D181" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="E181" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>39</v>
@@ -4972,19 +4993,19 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D183" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="B183" t="s" s="2">
+      <c r="E183" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="C183" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D183" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="E183" t="s" s="2">
-        <v>159</v>
       </c>
     </row>
     <row r="184">
@@ -4998,10 +5019,10 @@
         <v>39</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>243</v>
+        <v>159</v>
       </c>
     </row>
     <row r="185">
@@ -5015,27 +5036,27 @@
         <v>39</v>
       </c>
       <c r="D185" t="s" s="2">
-        <v>333</v>
+        <v>242</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>334</v>
+        <v>243</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D186" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="B186" t="s" s="2">
+      <c r="E186" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="C186" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D186" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="E186" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="187">
@@ -5083,10 +5104,10 @@
         <v>39</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>320</v>
+        <v>243</v>
       </c>
     </row>
     <row r="190">
@@ -5100,10 +5121,10 @@
         <v>39</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>243</v>
+        <v>322</v>
       </c>
     </row>
     <row r="191">
@@ -5168,18 +5189,18 @@
         <v>39</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>353</v>
+        <v>242</v>
       </c>
       <c r="E194" t="s" s="2">
-        <v>354</v>
+        <v>243</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C195" t="s" s="2">
         <v>39</v>
@@ -5193,19 +5214,19 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D196" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="B196" t="s" s="2">
+      <c r="E196" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D196" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="E196" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="197">
@@ -5219,10 +5240,10 @@
         <v>39</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>158</v>
+        <v>321</v>
       </c>
       <c r="E197" t="s" s="2">
-        <v>159</v>
+        <v>322</v>
       </c>
     </row>
     <row r="198">
@@ -5236,10 +5257,10 @@
         <v>39</v>
       </c>
       <c r="D198" t="s" s="2">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="E198" t="s" s="2">
-        <v>65</v>
+        <v>159</v>
       </c>
     </row>
     <row r="199">
@@ -5247,7 +5268,7 @@
         <v>363</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>364</v>
+        <v>107</v>
       </c>
       <c r="C199" t="s" s="2">
         <v>39</v>
@@ -5257,6 +5278,57 @@
       </c>
       <c r="E199" t="s" s="2">
         <v>65</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D200" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E200" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E201" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D202" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="E202" t="s" s="2">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5288,7 +5360,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>35</v>
@@ -5305,10 +5377,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>39</v>
@@ -5322,10 +5394,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>39</v>
@@ -5339,10 +5411,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>39</v>
@@ -5356,10 +5428,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>39</v>
@@ -5373,10 +5445,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>39</v>
@@ -5390,10 +5462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>39</v>
@@ -5407,10 +5479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>39</v>
@@ -5424,10 +5496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>39</v>
@@ -5441,10 +5513,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>39</v>
@@ -5458,10 +5530,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>39</v>
@@ -5475,10 +5547,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>39</v>
@@ -5492,10 +5564,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>39</v>
@@ -5509,10 +5581,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>39</v>
@@ -5526,10 +5598,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>39</v>
@@ -5543,10 +5615,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>39</v>
@@ -5560,10 +5632,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>39</v>
@@ -5577,10 +5649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>39</v>
@@ -5594,10 +5666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>39</v>
@@ -5611,10 +5683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>39</v>
@@ -5628,10 +5700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>39</v>
@@ -5645,10 +5717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>39</v>
@@ -5662,10 +5734,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>39</v>
@@ -5679,10 +5751,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>39</v>
@@ -5696,10 +5768,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>39</v>
@@ -5713,10 +5785,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>39</v>
@@ -5730,10 +5802,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>39</v>
@@ -5747,10 +5819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>39</v>
@@ -5764,10 +5836,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>39</v>
@@ -5781,10 +5853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>39</v>
@@ -5798,10 +5870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>39</v>
@@ -5815,10 +5887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>39</v>
@@ -5832,10 +5904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>39</v>
@@ -5849,10 +5921,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>39</v>
@@ -5866,10 +5938,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>39</v>
@@ -5883,10 +5955,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>39</v>
@@ -5900,10 +5972,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>39</v>
@@ -5917,10 +5989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>39</v>
@@ -5934,10 +6006,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>39</v>
@@ -5951,10 +6023,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>39</v>
@@ -5968,10 +6040,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>39</v>
@@ -5985,10 +6057,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>39</v>
@@ -6002,10 +6074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>39</v>
@@ -6019,10 +6091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>39</v>
@@ -6036,10 +6108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>39</v>
@@ -6053,10 +6125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>39</v>
@@ -6070,10 +6142,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>39</v>
@@ -6087,10 +6159,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>39</v>
@@ -6104,10 +6176,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>39</v>
@@ -6121,10 +6193,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>39</v>
@@ -6138,10 +6210,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>39</v>
@@ -6155,10 +6227,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>39</v>
@@ -6172,10 +6244,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>39</v>
@@ -6189,10 +6261,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>39</v>
@@ -6206,10 +6278,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>39</v>
@@ -6223,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>39</v>
@@ -6240,10 +6312,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>39</v>
@@ -6257,10 +6329,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>39</v>
@@ -6274,10 +6346,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>39</v>
@@ -6291,10 +6363,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>39</v>
@@ -6308,10 +6380,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>39</v>
@@ -6325,10 +6397,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>39</v>
@@ -6342,10 +6414,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>39</v>
@@ -6359,10 +6431,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>39</v>
@@ -6376,10 +6448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>39</v>
@@ -6393,10 +6465,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>39</v>
@@ -6410,10 +6482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>39</v>
@@ -6427,10 +6499,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>39</v>
@@ -6444,10 +6516,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>39</v>
@@ -6461,10 +6533,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>39</v>
@@ -6478,10 +6550,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>39</v>
@@ -6495,10 +6567,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>39</v>
@@ -6512,10 +6584,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>39</v>
@@ -6529,10 +6601,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>39</v>
@@ -6546,10 +6618,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>39</v>
@@ -6563,10 +6635,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>39</v>
@@ -6580,10 +6652,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>39</v>
@@ -6597,10 +6669,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>39</v>
@@ -6614,10 +6686,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>39</v>
@@ -6631,10 +6703,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>39</v>
@@ -6648,10 +6720,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>39</v>
@@ -6665,10 +6737,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>39</v>
@@ -6682,10 +6754,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>39</v>
@@ -6699,10 +6771,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>39</v>
@@ -6716,10 +6788,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>39</v>
@@ -6733,10 +6805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>39</v>
@@ -6750,10 +6822,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>39</v>
@@ -6767,10 +6839,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>39</v>
@@ -6784,10 +6856,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>39</v>
@@ -6801,10 +6873,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>39</v>
@@ -6818,10 +6890,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>39</v>
@@ -6835,10 +6907,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>39</v>
@@ -6852,10 +6924,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>39</v>
@@ -6869,10 +6941,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>39</v>
@@ -6886,10 +6958,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>39</v>
@@ -6903,10 +6975,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>39</v>
@@ -6920,10 +6992,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>39</v>
@@ -6937,10 +7009,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>39</v>
@@ -6954,10 +7026,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>39</v>
@@ -6971,10 +7043,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>39</v>
@@ -6988,10 +7060,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>39</v>
@@ -7005,10 +7077,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>39</v>
@@ -7022,10 +7094,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>39</v>
@@ -7039,10 +7111,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>39</v>
@@ -7056,10 +7128,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>39</v>
@@ -7073,10 +7145,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>39</v>
@@ -7090,10 +7162,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>39</v>
@@ -7107,10 +7179,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>39</v>
@@ -7124,10 +7196,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>39</v>
@@ -7141,10 +7213,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>39</v>
@@ -7158,10 +7230,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>39</v>
@@ -7175,27 +7247,27 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>39</v>
@@ -7209,10 +7281,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>39</v>
@@ -7226,10 +7298,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>39</v>
@@ -7243,10 +7315,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>39</v>
@@ -7260,10 +7332,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>39</v>
@@ -7277,10 +7349,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>39</v>
@@ -7294,10 +7366,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>39</v>
@@ -7311,10 +7383,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>39</v>
@@ -7328,10 +7400,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>39</v>
@@ -7345,10 +7417,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>39</v>
@@ -7362,10 +7434,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>39</v>
@@ -7379,10 +7451,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>39</v>
@@ -7396,10 +7468,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>39</v>
@@ -7413,10 +7485,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>39</v>
@@ -7430,10 +7502,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>39</v>
@@ -7447,10 +7519,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>39</v>
@@ -7464,27 +7536,27 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>39</v>
@@ -7498,10 +7570,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="C132" t="s" s="2">
         <v>39</v>
@@ -7515,10 +7587,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="C133" t="s" s="2">
         <v>39</v>
